--- a/artfynd/A 38448-2026 artfynd.xlsx
+++ b/artfynd/A 38448-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>70109338</v>
+        <v>136759753</v>
       </c>
       <c r="B2" t="n">
-        <v>106324</v>
+        <v>92106</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>600 m SSO om Hästtorpet, Brattelsöns ostsida, Upl</t>
+          <t>Rödmossa, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>594623</v>
+        <v>594587</v>
       </c>
       <c r="R2" t="n">
-        <v>6662000</v>
+        <v>6662138</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,17 +749,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1996-01-01</t>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1996-12-31</t>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Upplandsfloran - detaljuppgifter. Observatör Egil Wahlström</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,20 +784,349 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136759753</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136760030</v>
+      </c>
+      <c r="B3" t="n">
+        <v>92069</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Enåker, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>594640</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6661932</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Enåker</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136760030</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136760031</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92069</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Enåker, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>594571</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6661800</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Enåker</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136760031</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>70109338</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>600 m SSO om Hästtorpet, Brattelsöns ostsida, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>594623</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6662000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>100</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Enåker</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>1996-01-01</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1996-12-31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Upplandsfloran - detaljuppgifter. Observatör Egil Wahlström</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Mora Aronsson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Via Mora Aronsson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Upplands Flora 2010</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/70109338</t>
         </is>
@@ -792,6 +1135,9 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38448-2026 artfynd.xlsx
+++ b/artfynd/A 38448-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759753</v>
       </c>
       <c r="B2" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136760030</v>
       </c>
       <c r="B3" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136760031</v>
       </c>
       <c r="B4" t="n">
-        <v>92069</v>
+        <v>92074</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38448-2026 artfynd.xlsx
+++ b/artfynd/A 38448-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759753</v>
       </c>
       <c r="B2" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136760030</v>
       </c>
       <c r="B3" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136760031</v>
       </c>
       <c r="B4" t="n">
-        <v>92074</v>
+        <v>92076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38448-2026 artfynd.xlsx
+++ b/artfynd/A 38448-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759753</v>
       </c>
       <c r="B2" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136760030</v>
       </c>
       <c r="B3" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136760031</v>
       </c>
       <c r="B4" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38448-2026 artfynd.xlsx
+++ b/artfynd/A 38448-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759753</v>
       </c>
       <c r="B2" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136760030</v>
       </c>
       <c r="B3" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136760031</v>
       </c>
       <c r="B4" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38448-2026 artfynd.xlsx
+++ b/artfynd/A 38448-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759753</v>
       </c>
       <c r="B2" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136760030</v>
       </c>
       <c r="B3" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136760031</v>
       </c>
       <c r="B4" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38448-2026 artfynd.xlsx
+++ b/artfynd/A 38448-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759753</v>
       </c>
       <c r="B2" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136760030</v>
       </c>
       <c r="B3" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136760031</v>
       </c>
       <c r="B4" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38448-2026 artfynd.xlsx
+++ b/artfynd/A 38448-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759753</v>
       </c>
       <c r="B2" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136760030</v>
       </c>
       <c r="B3" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136760031</v>
       </c>
       <c r="B4" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38448-2026 artfynd.xlsx
+++ b/artfynd/A 38448-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759753</v>
       </c>
       <c r="B2" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136760030</v>
       </c>
       <c r="B3" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136760031</v>
       </c>
       <c r="B4" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38448-2026 artfynd.xlsx
+++ b/artfynd/A 38448-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759753</v>
       </c>
       <c r="B2" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136760030</v>
       </c>
       <c r="B3" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136760031</v>
       </c>
       <c r="B4" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38448-2026 artfynd.xlsx
+++ b/artfynd/A 38448-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759753</v>
       </c>
       <c r="B2" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136760030</v>
       </c>
       <c r="B3" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136760031</v>
       </c>
       <c r="B4" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38448-2026 artfynd.xlsx
+++ b/artfynd/A 38448-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759753</v>
       </c>
       <c r="B2" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136760030</v>
       </c>
       <c r="B3" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136760031</v>
       </c>
       <c r="B4" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38448-2026 artfynd.xlsx
+++ b/artfynd/A 38448-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759753</v>
       </c>
       <c r="B2" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136760030</v>
       </c>
       <c r="B3" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136760031</v>
       </c>
       <c r="B4" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 38448-2026 artfynd.xlsx
+++ b/artfynd/A 38448-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759753</v>
       </c>
       <c r="B2" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136760030</v>
       </c>
       <c r="B3" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>136760031</v>
       </c>
       <c r="B4" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
